--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261007.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261007.xlsx
@@ -123,12 +123,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF1FB"/>
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
+        <fgColor rgb="00EAF1FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -167,17 +167,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,7 +190,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -227,7 +227,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -236,13 +239,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.5256198347107438</v>
+        <v>0.5380165289256198</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.008090909090909051</v>
+        <v>0.0204876033057851</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>おおむね予定どおり 31件／前倒し 9件／期限超過（1か月） 5件／遅れ 3件／期限超過（2か月） 1件</t>
+          <t>おおむね予定どおり 31件／前倒し 10件／期限超過（1か月） 5件／遅れ 2件／期限超過（2か月） 1件</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$50,$A2,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A2)*'01_WBS'!$M$2:$M$50)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A2)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A2)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -2758,7 +2758,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$50,$A3,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A3)*'01_WBS'!$M$2:$M$50)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A3)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A3)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -2803,7 +2803,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$50,$A4,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A4)*'01_WBS'!$M$2:$M$50)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A4)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A4)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -2848,7 +2848,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$50,$A5,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A5)*'01_WBS'!$M$2:$M$50)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A5)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A5)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -2893,7 +2893,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$50,$A6,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A6)*'01_WBS'!$M$2:$M$50)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A6)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A6)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -2938,7 +2938,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$50,$A7,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A7)*'01_WBS'!$M$2:$M$50)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A7)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A7)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -2983,7 +2983,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$50,$A8,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A8)*'01_WBS'!$M$2:$M$50)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A8)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$E$2:$E$50=$A8)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -2994,37 +2994,37 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr"/>
-      <c r="C9" s="27">
+      <c r="B9" s="27" t="inlineStr"/>
+      <c r="C9" s="28">
         <f>SUM(C2:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <f>SUM(D2:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="28">
         <f>SUM(E2:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="28">
         <f>SUM(F2:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="28">
         <f>SUM(G2:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="28">
         <f>SUM(H2:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="29">
         <f>IF(SUM('01_WBS'!$M$2:$M$50)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$50,'01_WBS'!$M$2:$M$50)/SUM('01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -3176,13 +3176,13 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H2" s="29" t="n">
+      <c r="H2" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="29" t="n">
+      <c r="I2" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J2" s="29" t="n">
+      <c r="J2" s="30" t="n">
         <v>-100</v>
       </c>
       <c r="K2" s="19" t="n">
@@ -3235,13 +3235,13 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H3" s="29" t="n">
+      <c r="H3" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="29" t="n">
+      <c r="I3" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J3" s="29" t="n">
+      <c r="J3" s="30" t="n">
         <v>-100</v>
       </c>
       <c r="K3" s="19" t="n">
@@ -3294,13 +3294,13 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H4" s="29" t="n">
+      <c r="H4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="29" t="n">
+      <c r="I4" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J4" s="29" t="n">
+      <c r="J4" s="30" t="n">
         <v>-100</v>
       </c>
       <c r="K4" s="19" t="n">
@@ -3353,19 +3353,19 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H5" s="29" t="n">
+      <c r="H5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="29" t="n">
+      <c r="I5" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="J5" s="29" t="n">
+      <c r="J5" s="30" t="n">
         <v>-60</v>
       </c>
       <c r="K5" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L5" s="30" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>遅れ</t>
         </is>
@@ -3412,13 +3412,13 @@
           <t>要対応</t>
         </is>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="I6" s="29" t="n">
+      <c r="I6" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="30" t="n">
         <v>-60</v>
       </c>
       <c r="K6" s="19" t="n">
@@ -3471,13 +3471,13 @@
           <t>要対応</t>
         </is>
       </c>
-      <c r="H7" s="29" t="n">
+      <c r="H7" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="I7" s="29" t="n">
+      <c r="I7" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J7" s="29" t="n">
+      <c r="J7" s="30" t="n">
         <v>-50</v>
       </c>
       <c r="K7" s="19" t="n">
@@ -3530,13 +3530,13 @@
           <t>要対応</t>
         </is>
       </c>
-      <c r="H8" s="29" t="n">
+      <c r="H8" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="I8" s="29" t="n">
+      <c r="I8" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="J8" s="30" t="n">
         <v>-20</v>
       </c>
       <c r="K8" s="19" t="n">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>2-15</t>
+          <t>2-16</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>介護保険の利用の有無による問31の再集計</t>
+          <t>確認票の2枚化（町向け・事業所向け）</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -3589,43 +3589,43 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H9" s="29" t="n">
+      <c r="H9" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="29" t="n">
+      <c r="I9" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="J9" s="29" t="n">
+      <c r="J9" s="30" t="n">
         <v>-20</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="30" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L9" s="25" t="inlineStr">
         <is>
           <t>遅れ</t>
         </is>
       </c>
       <c r="M9" s="18" t="inlineStr">
         <is>
-          <t>**なし（当方で実施可能）**</t>
+          <t>2-15の結果（短期入所の照会の主題が変わる）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>2-16</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>確認票の2枚化（町向け・事業所向け）</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -3635,56 +3635,56 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="J10" s="29" t="n">
-        <v>-20</v>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="n">
+        <v>60</v>
+      </c>
+      <c r="I10" s="30" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="J10" s="30" t="n">
+        <v>-4.5</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="30" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+        <v>3</v>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>おおむね予定どおり</t>
         </is>
       </c>
       <c r="M10" s="18" t="inlineStr">
         <is>
-          <t>2-15の結果（短期入所の照会の主題が変わる）</t>
+          <t>調査結果の反映</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>現行計画の取組み状況の検証</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -3707,14 +3707,14 @@
           <t>進行中</t>
         </is>
       </c>
-      <c r="H11" s="29" t="n">
-        <v>60</v>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J11" s="29" t="n">
-        <v>-4.5</v>
+      <c r="H11" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="I11" s="30" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="J11" s="30" t="n">
+        <v>-3.6</v>
       </c>
       <c r="K11" s="19" t="n">
         <v>3</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M11" s="18" t="inlineStr">
         <is>
-          <t>調査結果の反映</t>
+          <t>**前回計画31項目の令和8年度末の実績（依頼票D6）。**目標値は受領済みのため、残るのは実績のみ</t>
         </is>
       </c>
     </row>
@@ -3738,17 +3738,17 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>現行計画の取組み状況の検証</t>
+          <t>人口推計の出典の統一</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -3761,22 +3761,22 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="H12" s="29" t="n">
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="H12" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="I12" s="29" t="n">
+      <c r="I12" s="30" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="J12" s="29" t="n">
+      <c r="J12" s="30" t="n">
         <v>-3.6</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -3785,29 +3785,29 @@
       </c>
       <c r="M12" s="18" t="inlineStr">
         <is>
-          <t>**前回計画31項目の令和8年度末の実績（依頼票D6）。**目標値は受領済みのため、残るのは実績のみ</t>
+          <t>**町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと**</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>人口推計の出典の統一</t>
+          <t>自立支援協議会への出席（3回）</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
@@ -3817,25 +3817,25 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>要対応</t>
-        </is>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>70</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>-3.6</v>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="30" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>-1.8</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -3844,24 +3844,24 @@
       </c>
       <c r="M13" s="18" t="inlineStr">
         <is>
-          <t>**町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと**</t>
+          <t>第2回・第3回の時期は工程変更の協議による</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>自立支援協議会への出席（3回）</t>
+          <t>調査票の作成と補修正</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -3876,25 +3876,25 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>-1.8</v>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="H14" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="I14" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="K14" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -3903,24 +3903,24 @@
       </c>
       <c r="M14" s="18" t="inlineStr">
         <is>
-          <t>第2回・第3回の時期は工程変更の協議による</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>調査票の作成と補修正</t>
+          <t>委託仕様書の確認と適合性チェック</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -3943,17 +3943,17 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H15" s="29" t="n">
+      <c r="H15" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I15" s="29" t="n">
+      <c r="I15" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J15" s="29" t="n">
+      <c r="J15" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
@@ -3969,17 +3969,17 @@
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>委託仕様書の確認と適合性チェック</t>
+          <t>調査内容の企画</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -4002,13 +4002,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H16" s="29" t="n">
+      <c r="H16" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I16" s="29" t="n">
+      <c r="I16" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J16" s="29" t="n">
+      <c r="J16" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="19" t="n">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>調査内容の企画</t>
+          <t>調査実施設計</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -4048,12 +4048,12 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -4061,13 +4061,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H17" s="29" t="n">
+      <c r="H17" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I17" s="29" t="n">
+      <c r="I17" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J17" s="29" t="n">
+      <c r="J17" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="19" t="n">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>調査実施設計</t>
+          <t>調査の発送・回収</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -4120,13 +4120,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H18" s="29" t="n">
+      <c r="H18" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I18" s="29" t="n">
+      <c r="I18" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J18" s="29" t="n">
+      <c r="J18" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="19" t="n">
@@ -4146,17 +4146,17 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>調査の発送・回収</t>
+          <t>実施計画と質問票の作成</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -4179,13 +4179,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H19" s="29" t="n">
+      <c r="H19" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I19" s="29" t="n">
+      <c r="I19" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J19" s="29" t="n">
+      <c r="J19" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="19" t="n">
@@ -4205,17 +4205,17 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>実施計画と質問票の作成</t>
+          <t>手帳所持者・サービス利用状況の分析</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -4225,26 +4225,26 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="J20" s="29" t="n">
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="H20" s="30" t="n">
+        <v>60</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="19" t="n">
@@ -4257,24 +4257,24 @@
       </c>
       <c r="M20" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>手帳所持者・サービス利用状況の分析</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -4284,26 +4284,26 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G21" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="H21" s="29" t="n">
-        <v>60</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>60</v>
-      </c>
-      <c r="J21" s="29" t="n">
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="19" t="n">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="M21" s="18" t="inlineStr">
         <is>
-          <t>**支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要**</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -4328,12 +4328,12 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>レイアウトデザイン・イラスト起こし</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -4356,13 +4356,13 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H22" s="29" t="n">
+      <c r="H22" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="29" t="n">
+      <c r="I22" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="29" t="n">
+      <c r="J22" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="19" t="n">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="M22" s="18" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・イラスト起こし</t>
+          <t>契約・体制の確立、キックオフ</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -4402,30 +4402,30 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G23" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H23" s="29" t="n">
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="H23" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="29" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="M23" s="18" t="inlineStr">
         <is>
-          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -4446,12 +4446,12 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>契約・体制の確立、キックオフ</t>
+          <t>現行計画（第7期・第3期）の確認</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -4474,13 +4474,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H24" s="29" t="n">
+      <c r="H24" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I24" s="29" t="n">
+      <c r="I24" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J24" s="29" t="n">
+      <c r="J24" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="19" t="n">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>現行計画（第7期・第3期）の確認</t>
+          <t>第3期地域福祉計画との役割分担の整理</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
@@ -4533,13 +4533,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H25" s="29" t="n">
+      <c r="H25" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I25" s="29" t="n">
+      <c r="I25" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J25" s="29" t="n">
+      <c r="J25" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="19" t="n">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画との役割分担の整理</t>
+          <t>町への資料依頼票の作成</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
@@ -4592,13 +4592,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H26" s="29" t="n">
+      <c r="H26" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I26" s="29" t="n">
+      <c r="I26" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J26" s="29" t="n">
+      <c r="J26" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="19" t="n">
@@ -4618,17 +4618,17 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>町への資料依頼票の作成</t>
+          <t>調査用品の準備・印刷</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -4651,13 +4651,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H27" s="29" t="n">
+      <c r="H27" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I27" s="29" t="n">
+      <c r="I27" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J27" s="29" t="n">
+      <c r="J27" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="19" t="n">
@@ -4677,17 +4677,17 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>調査用品の準備・印刷</t>
+          <t>記録の作成と対象先への確認</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
@@ -4697,26 +4697,26 @@
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="H28" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="I28" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="J28" s="29" t="n">
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H28" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="19" t="n">
@@ -4729,39 +4729,39 @@
       </c>
       <c r="M28" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>記録の作成と対象先への確認</t>
+          <t>骨子案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -4769,13 +4769,13 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H29" s="29" t="n">
+      <c r="H29" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="29" t="n">
+      <c r="I29" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="29" t="n">
+      <c r="J29" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="19" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="M29" s="18" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>工程変更の合意</t>
         </is>
       </c>
     </row>
@@ -4800,12 +4800,12 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-6</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>骨子案の協議（自立支援協議会）</t>
+          <t>素案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -4828,13 +4828,13 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H30" s="29" t="n">
+      <c r="H30" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="29" t="n">
+      <c r="I30" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="29" t="n">
+      <c r="J30" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="19" t="n">
@@ -4847,39 +4847,39 @@
       </c>
       <c r="M30" s="18" t="inlineStr">
         <is>
-          <t>工程変更の合意</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>素案の協議（自立支援協議会）</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -4887,13 +4887,13 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H31" s="29" t="n">
+      <c r="H31" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="29" t="n">
+      <c r="I31" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="29" t="n">
+      <c r="J31" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="19" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="M31" s="18" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -4918,27 +4918,27 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
@@ -4946,13 +4946,13 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H32" s="29" t="n">
+      <c r="H32" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="29" t="n">
+      <c r="I32" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="29" t="n">
+      <c r="J32" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="19" t="n">
@@ -4965,24 +4965,24 @@
       </c>
       <c r="M32" s="18" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>リライト作業</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
@@ -5005,13 +5005,13 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H33" s="29" t="n">
+      <c r="H33" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I33" s="29" t="n">
+      <c r="I33" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="29" t="n">
+      <c r="J33" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="19" t="n">
@@ -5024,57 +5024,57 @@
       </c>
       <c r="M33" s="18" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>計画案の確定</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>リライト作業</t>
+          <t>調査票原案の町の確認</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G34" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H34" s="29" t="n">
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="H34" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="J34" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="29" t="n">
-        <v>0</v>
-      </c>
       <c r="K34" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" s="20" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="M34" s="18" t="inlineStr">
         <is>
-          <t>計画案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -5095,27 +5095,27 @@
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>調査票原案の町の確認</t>
+          <t>宛名ラベルの作成</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F35" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -5123,13 +5123,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H35" s="29" t="n">
+      <c r="H35" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I35" s="29" t="n">
+      <c r="I35" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J35" s="29" t="n">
+      <c r="J35" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="19" t="n">
@@ -5149,46 +5149,46 @@
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>宛名ラベルの作成</t>
+          <t>町による報告書の確認</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G36" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="H36" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="J36" s="29" t="n">
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H36" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="19" t="n">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M36" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の作成</t>
         </is>
       </c>
     </row>
@@ -5213,17 +5213,17 @@
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>町による報告書の確認</t>
+          <t>報告書の完成・納品</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E37" s="19" t="inlineStr">
@@ -5241,13 +5241,13 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="H37" s="29" t="n">
+      <c r="H37" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="29" t="n">
+      <c r="I37" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="29" t="n">
+      <c r="J37" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="19" t="n">
@@ -5260,24 +5260,24 @@
       </c>
       <c r="M37" s="18" t="inlineStr">
         <is>
-          <t>報告書の作成</t>
+          <t>町の確認</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>報告書の完成・納品</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
@@ -5287,26 +5287,26 @@
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H38" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="29" t="n">
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="H38" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="J38" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="19" t="n">
@@ -5319,53 +5319,53 @@
       </c>
       <c r="M38" s="18" t="inlineStr">
         <is>
-          <t>町の確認</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G39" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="H39" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="I39" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="J39" s="29" t="n">
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H39" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="19" t="n">
@@ -5378,24 +5378,24 @@
       </c>
       <c r="M39" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）**</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
@@ -5405,30 +5405,30 @@
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H40" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="29" t="n">
-        <v>0</v>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="H40" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="30" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="J40" s="30" t="n">
+        <v>0.2</v>
       </c>
       <c r="K40" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L40" s="20" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="M40" s="18" t="inlineStr">
         <is>
-          <t>**完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）**</t>
+          <t>**基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
         </is>
       </c>
     </row>
@@ -5449,17 +5449,17 @@
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E41" s="19" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="F41" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G41" s="22" t="inlineStr">
@@ -5477,26 +5477,26 @@
           <t>進行中</t>
         </is>
       </c>
-      <c r="H41" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="I41" s="29" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="J41" s="29" t="n">
-        <v>0.2</v>
+      <c r="H41" s="30" t="n">
+        <v>40</v>
+      </c>
+      <c r="I41" s="30" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J41" s="30" t="n">
+        <v>16.3</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L41" s="20" t="inlineStr">
-        <is>
-          <t>おおむね予定どおり</t>
+        <v>4</v>
+      </c>
+      <c r="L41" s="31" t="inlineStr">
+        <is>
+          <t>前倒し</t>
         </is>
       </c>
       <c r="M41" s="18" t="inlineStr">
         <is>
-          <t>**基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
+          <t>**A-1〜A-5の解消。とくに地域生活支援事業のR6〜R8実績（法定記載事項）と、居宅介護R7の113時間が実績か入力誤りかの確認**</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>サービス見込量の算定</t>
+          <t>素案の作成</t>
         </is>
       </c>
       <c r="D42" s="19" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
@@ -5536,17 +5536,17 @@
           <t>進行中</t>
         </is>
       </c>
-      <c r="H42" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="I42" s="29" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="J42" s="29" t="n">
-        <v>16.3</v>
+      <c r="H42" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="30" t="n">
+        <v>30</v>
       </c>
       <c r="K42" s="19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L42" s="31" t="inlineStr">
         <is>
@@ -5555,24 +5555,24 @@
       </c>
       <c r="M42" s="18" t="inlineStr">
         <is>
-          <t>**A-1〜A-5の解消。とくに地域生活支援事業のR6〜R8実績（法定記載事項）と、居宅介護R7の113時間が実績か入力誤りかの確認**</t>
+          <t>**条件なしで着手できる。調査結果を待たずに構成・本文は書ける**</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>2-11</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>素案の作成</t>
+          <t>集計・分析</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G43" s="22" t="inlineStr">
@@ -5595,17 +5595,17 @@
           <t>進行中</t>
         </is>
       </c>
-      <c r="H43" s="29" t="n">
+      <c r="H43" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="I43" s="30" t="n">
+        <v>40</v>
+      </c>
+      <c r="J43" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="I43" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="29" t="n">
-        <v>30</v>
-      </c>
       <c r="K43" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L43" s="31" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M43" s="18" t="inlineStr">
         <is>
-          <t>**条件なしで着手できる。調査結果を待たずに構成・本文は書ける**</t>
+          <t>**レビュー所見の反映（重大5件）。**うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
         </is>
       </c>
     </row>
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>2-11</t>
+          <t>2-15</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>集計・分析</t>
+          <t>介護保険の利用の有無による問31の再集計</t>
         </is>
       </c>
       <c r="D44" s="19" t="inlineStr">
@@ -5641,26 +5641,26 @@
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="F44" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="G44" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="H44" s="29" t="n">
-        <v>70</v>
-      </c>
-      <c r="I44" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="J44" s="29" t="n">
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G44" s="25" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
+        </is>
+      </c>
+      <c r="H44" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="I44" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="J44" s="30" t="n">
         <v>30</v>
       </c>
       <c r="K44" s="19" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="M44" s="18" t="inlineStr">
         <is>
-          <t>**レビュー所見の反映（重大5件）。**うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
+          <t>**個票（1件ごとの回答データ）。**集計表は集計結果だけで個票がなく、問29×問31のクロス集計が作れない（依頼票D7）</t>
         </is>
       </c>
     </row>
@@ -5713,13 +5713,13 @@
           <t>進行中</t>
         </is>
       </c>
-      <c r="H45" s="29" t="n">
+      <c r="H45" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="I45" s="29" t="n">
+      <c r="I45" s="30" t="n">
         <v>6.6</v>
       </c>
-      <c r="J45" s="29" t="n">
+      <c r="J45" s="30" t="n">
         <v>33.4</v>
       </c>
       <c r="K45" s="19" t="n">
@@ -5772,13 +5772,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H46" s="29" t="n">
+      <c r="H46" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I46" s="29" t="n">
+      <c r="I46" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="J46" s="29" t="n">
+      <c r="J46" s="30" t="n">
         <v>40</v>
       </c>
       <c r="K46" s="19" t="n">
@@ -5831,13 +5831,13 @@
           <t>進行中</t>
         </is>
       </c>
-      <c r="H47" s="29" t="n">
+      <c r="H47" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="I47" s="29" t="n">
+      <c r="I47" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="29" t="n">
+      <c r="J47" s="30" t="n">
         <v>40</v>
       </c>
       <c r="K47" s="19" t="n">
@@ -5890,13 +5890,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H48" s="29" t="n">
+      <c r="H48" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I48" s="29" t="n">
+      <c r="I48" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="J48" s="29" t="n">
+      <c r="J48" s="30" t="n">
         <v>80</v>
       </c>
       <c r="K48" s="19" t="n">
@@ -5949,13 +5949,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H49" s="29" t="n">
+      <c r="H49" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I49" s="29" t="n">
+      <c r="I49" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="J49" s="29" t="n">
+      <c r="J49" s="30" t="n">
         <v>80</v>
       </c>
       <c r="K49" s="19" t="n">
@@ -6008,13 +6008,13 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="H50" s="29" t="n">
+      <c r="H50" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I50" s="29" t="n">
+      <c r="I50" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="J50" s="29" t="n">
+      <c r="J50" s="30" t="n">
         <v>80</v>
       </c>
       <c r="K50" s="19" t="n">
@@ -6034,7 +6034,7 @@
     <row r="52">
       <c r="A52" s="32" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 52.6％　対　予定進捗率 51.8％　乖離 +0.8ポイント</t>
+          <t>加重の実績進捗率 53.8％　対　予定進捗率 51.8％　乖離 +2.0ポイント</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
     <row r="54">
       <c r="A54" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">　遅れ 3件</t>
+          <t xml:space="preserve">　遅れ 2件</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
     <row r="56">
       <c r="A56" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">　前倒し 9件</t>
+          <t xml:space="preserve">　前倒し 10件</t>
         </is>
       </c>
     </row>
@@ -7790,25 +7790,25 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K23" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K23" s="25" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="L23" s="21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M23" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N23" s="18" t="inlineStr">
         <is>
-          <t>**2-14で必要と判定。既存データでできるため追加調査は不要。**介護保険利用者77人を除いた182人で取り直し、給付実績に近づくかを見る</t>
+          <t>**周辺度数による切り分けを令和8年10月7日に実施（23_障がいアンケート分析）。**上振れ58人のうち49人は介護保険との取り違えで説明しうるが、**9人（重度包括5・就労選択2・同行援護1・就労移行1）は説明できない。**問28の無回答77人と問29の介護保険利用77人が完全一致することも確認</t>
         </is>
       </c>
       <c r="O23" s="18" t="inlineStr">
         <is>
-          <t>**なし（当方で実施可能）**</t>
+          <t>**個票（1件ごとの回答データ）。**集計表は集計結果だけで個票がなく、問29×問31のクロス集計が作れない（依頼票D7）</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9919,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$50,$A2,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="H2" s="25">
+      <c r="H2" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A2)*'01_WBS'!$M$2:$M$50)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A2)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A2)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -9969,7 +9969,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$50,$A3,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A3)*'01_WBS'!$M$2:$M$50)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A3)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A3)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -10019,7 +10019,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$50,$A4,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A4)*'01_WBS'!$M$2:$M$50)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A4)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A4)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -10069,7 +10069,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$50,$A5,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A5)*'01_WBS'!$M$2:$M$50)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A5)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A5)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -10119,7 +10119,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$50,$A6,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A6)*'01_WBS'!$M$2:$M$50)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A6)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A6)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -10169,7 +10169,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$50,$A7,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A7)*'01_WBS'!$M$2:$M$50)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A7)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A7)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -10219,7 +10219,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$50,$A8,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A8)*'01_WBS'!$M$2:$M$50)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A8)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A8)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -10269,7 +10269,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$50,$A9,'01_WBS'!$K$2:$K$50,"未着手")</f>
         <v/>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="26">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A9)*'01_WBS'!$M$2:$M$50)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A9)*'01_WBS'!$L$2:$L$50*'01_WBS'!$M$2:$M$50)/SUMPRODUCT(('01_WBS'!$A$2:$A$50=$A9)*'01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>
@@ -10290,36 +10290,36 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="28">
         <f>SUM(B2:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="28">
         <f>SUM(C2:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <f>SUM(D2:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <f>SUM(E2:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="28">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="28">
         <f>SUM(G2:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>IF(SUM('01_WBS'!$M$2:$M$50)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$50,'01_WBS'!$M$2:$M$50)/SUM('01_WBS'!$M$2:$M$50)/100)</f>
         <v/>
       </c>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261007.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261007.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.5380165289256198</v>
+        <v>0.5545454545454546</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.0204876033057851</v>
+        <v>0.03701652892561981</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>おおむね予定どおり 31件／前倒し 10件／期限超過（1か月） 5件／遅れ 2件／期限超過（2か月） 1件</t>
+          <t>おおむね予定どおり 31件／前倒し 11件／期限超過（1か月） 5件／期限超過（2か月） 1件／遅れ 1件</t>
         </is>
       </c>
     </row>
@@ -3556,17 +3556,17 @@
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>2-16</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>確認票の2枚化（町向け・事業所向け）</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -3576,56 +3576,56 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H9" s="30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I9" s="30" t="n">
-        <v>20</v>
+        <v>64.5</v>
       </c>
       <c r="J9" s="30" t="n">
-        <v>-20</v>
+        <v>-4.5</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="25" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+        <v>3</v>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>おおむね予定どおり</t>
         </is>
       </c>
       <c r="M9" s="18" t="inlineStr">
         <is>
-          <t>2-15の結果（短期入所の照会の主題が変わる）</t>
+          <t>調査結果の反映</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>現行計画の取組み状況の検証</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -3649,13 +3649,13 @@
         </is>
       </c>
       <c r="H10" s="30" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I10" s="30" t="n">
-        <v>64.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>-4.5</v>
+        <v>-3.6</v>
       </c>
       <c r="K10" s="19" t="n">
         <v>3</v>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="M10" s="18" t="inlineStr">
         <is>
-          <t>調査結果の反映</t>
+          <t>**前回計画31項目の令和8年度末の実績（依頼票D6）。**目標値は受領済みのため、残るのは実績のみ</t>
         </is>
       </c>
     </row>
@@ -3679,17 +3679,17 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>現行計画の取組み状況の検証</t>
+          <t>人口推計の出典の統一</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
@@ -3702,9 +3702,9 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="H11" s="30" t="n">
@@ -3717,7 +3717,7 @@
         <v>-3.6</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L11" s="20" t="inlineStr">
         <is>
@@ -3726,29 +3726,29 @@
       </c>
       <c r="M11" s="18" t="inlineStr">
         <is>
-          <t>**前回計画31項目の令和8年度末の実績（依頼票D6）。**目標値は受領済みのため、残るのは実績のみ</t>
+          <t>**町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと**</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>人口推計の出典の統一</t>
+          <t>自立支援協議会への出席（3回）</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -3758,25 +3758,25 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G12" s="24" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H12" s="30" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="I12" s="30" t="n">
-        <v>73.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="J12" s="30" t="n">
-        <v>-3.6</v>
+        <v>-1.8</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -3785,24 +3785,24 @@
       </c>
       <c r="M12" s="18" t="inlineStr">
         <is>
-          <t>**町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと**</t>
+          <t>第2回・第3回の時期は工程変更の協議による</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>自立支援協議会への出席（3回）</t>
+          <t>調査票の作成と補修正</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -3817,25 +3817,25 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H13" s="30" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I13" s="30" t="n">
-        <v>31.8</v>
+        <v>100</v>
       </c>
       <c r="J13" s="30" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -3844,24 +3844,24 @@
       </c>
       <c r="M13" s="18" t="inlineStr">
         <is>
-          <t>第2回・第3回の時期は工程変更の協議による</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>調査票の作成と補修正</t>
+          <t>委託仕様書の確認と適合性チェック</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -3910,17 +3910,17 @@
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>委託仕様書の確認と適合性チェック</t>
+          <t>調査内容の企画</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>調査内容の企画</t>
+          <t>調査実施設計</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>調査実施設計</t>
+          <t>調査の発送・回収</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -4087,17 +4087,17 @@
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>調査の発送・回収</t>
+          <t>実施計画と質問票の作成</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -4146,17 +4146,17 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>実施計画と質問票の作成</t>
+          <t>手帳所持者・サービス利用状況の分析</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -4166,24 +4166,24 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H19" s="30" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I19" s="30" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J19" s="30" t="n">
         <v>0</v>
@@ -4198,24 +4198,24 @@
       </c>
       <c r="M19" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要**</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>手帳所持者・サービス利用状況の分析</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -4225,24 +4225,24 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I20" s="30" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J20" s="30" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="M20" s="18" t="inlineStr">
         <is>
-          <t>**支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要**</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>レイアウトデザイン・イラスト起こし</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -4316,24 +4316,24 @@
       </c>
       <c r="M21" s="18" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・イラスト起こし</t>
+          <t>契約・体制の確立、キックオフ</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
@@ -4343,30 +4343,30 @@
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G22" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H22" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="M22" s="18" t="inlineStr">
         <is>
-          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -4387,12 +4387,12 @@
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>契約・体制の確立、キックオフ</t>
+          <t>現行計画（第7期・第3期）の確認</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>現行計画（第7期・第3期）の確認</t>
+          <t>第3期地域福祉計画との役割分担の整理</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画との役割分担の整理</t>
+          <t>町への資料依頼票の作成</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
@@ -4559,17 +4559,17 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>町への資料依頼票の作成</t>
+          <t>調査用品の準備・印刷</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -4618,17 +4618,17 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>調査用品の準備・印刷</t>
+          <t>記録の作成と対象先への確認</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
@@ -4638,24 +4638,24 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H27" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J27" s="30" t="n">
         <v>0</v>
@@ -4670,39 +4670,39 @@
       </c>
       <c r="M27" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>記録の作成と対象先への確認</t>
+          <t>骨子案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="M28" s="18" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>工程変更の合意</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-6</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>骨子案の協議（自立支援協議会）</t>
+          <t>素案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -4788,39 +4788,39 @@
       </c>
       <c r="M29" s="18" t="inlineStr">
         <is>
-          <t>工程変更の合意</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>素案の協議（自立支援協議会）</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="M30" s="18" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -4859,27 +4859,27 @@
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="M31" s="18" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>リライト作業</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
@@ -4933,12 +4933,12 @@
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
@@ -4965,57 +4965,57 @@
       </c>
       <c r="M32" s="18" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>計画案の確定</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>リライト作業</t>
+          <t>調査票原案の町の確認</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G33" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H33" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33" s="30" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="20" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M33" s="18" t="inlineStr">
         <is>
-          <t>計画案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -5036,27 +5036,27 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>調査票原案の町の確認</t>
+          <t>宛名ラベルの作成</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -5090,44 +5090,44 @@
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>宛名ラベルの作成</t>
+          <t>町による報告書の確認</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F35" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G35" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H35" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I35" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J35" s="30" t="n">
         <v>0</v>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="M35" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の作成</t>
         </is>
       </c>
     </row>
@@ -5154,17 +5154,17 @@
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>町による報告書の確認</t>
+          <t>報告書の完成・納品</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
@@ -5201,24 +5201,24 @@
       </c>
       <c r="M36" s="18" t="inlineStr">
         <is>
-          <t>報告書の作成</t>
+          <t>町の確認</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>報告書の完成・納品</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
@@ -5228,24 +5228,24 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F37" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H37" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I37" s="30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J37" s="30" t="n">
         <v>0</v>
@@ -5260,51 +5260,51 @@
       </c>
       <c r="M37" s="18" t="inlineStr">
         <is>
-          <t>町の確認</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G38" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H38" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I38" s="30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J38" s="30" t="n">
         <v>0</v>
@@ -5319,24 +5319,24 @@
       </c>
       <c r="M38" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）**</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
@@ -5346,30 +5346,30 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H39" s="30" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I39" s="30" t="n">
-        <v>0</v>
+        <v>29.8</v>
       </c>
       <c r="J39" s="30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L39" s="20" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="M39" s="18" t="inlineStr">
         <is>
-          <t>**完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）**</t>
+          <t>**基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
         </is>
       </c>
     </row>
@@ -5390,17 +5390,17 @@
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G40" s="22" t="inlineStr">
@@ -5419,25 +5419,25 @@
         </is>
       </c>
       <c r="H40" s="30" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I40" s="30" t="n">
-        <v>29.8</v>
+        <v>23.7</v>
       </c>
       <c r="J40" s="30" t="n">
-        <v>0.2</v>
+        <v>16.3</v>
       </c>
       <c r="K40" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L40" s="20" t="inlineStr">
-        <is>
-          <t>おおむね予定どおり</t>
+        <v>4</v>
+      </c>
+      <c r="L40" s="31" t="inlineStr">
+        <is>
+          <t>前倒し</t>
         </is>
       </c>
       <c r="M40" s="18" t="inlineStr">
         <is>
-          <t>**基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
+          <t>**A-1〜A-5の解消。とくに地域生活支援事業のR6〜R8実績（法定記載事項）と、居宅介護R7の113時間が実績か入力誤りかの確認**</t>
         </is>
       </c>
     </row>
@@ -5449,12 +5449,12 @@
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>サービス見込量の算定</t>
+          <t>素案の作成</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F41" s="19" t="inlineStr">
@@ -5478,16 +5478,16 @@
         </is>
       </c>
       <c r="H41" s="30" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I41" s="30" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="J41" s="30" t="n">
-        <v>16.3</v>
+        <v>30</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L41" s="31" t="inlineStr">
         <is>
@@ -5496,24 +5496,24 @@
       </c>
       <c r="M41" s="18" t="inlineStr">
         <is>
-          <t>**A-1〜A-5の解消。とくに地域生活支援事業のR6〜R8実績（法定記載事項）と、居宅介護R7の113時間が実績か入力誤りかの確認**</t>
+          <t>**条件なしで着手できる。調査結果を待たずに構成・本文は書ける**</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>2-11</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>素案の作成</t>
+          <t>集計・分析</t>
         </is>
       </c>
       <c r="D42" s="19" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G42" s="22" t="inlineStr">
@@ -5537,16 +5537,16 @@
         </is>
       </c>
       <c r="H42" s="30" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="I42" s="30" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J42" s="30" t="n">
         <v>30</v>
       </c>
       <c r="K42" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L42" s="31" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="M42" s="18" t="inlineStr">
         <is>
-          <t>**条件なしで着手できる。調査結果を待たずに構成・本文は書ける**</t>
+          <t>**レビュー所見の反映（重大5件）。**うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5567,12 @@
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>2-11</t>
+          <t>2-15</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>集計・分析</t>
+          <t>介護保険の利用の有無による問31の再集計</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -5582,24 +5582,24 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="G43" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G43" s="25" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="H43" s="30" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="I43" s="30" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J43" s="30" t="n">
         <v>30</v>
@@ -5614,24 +5614,24 @@
       </c>
       <c r="M43" s="18" t="inlineStr">
         <is>
-          <t>**レビュー所見の反映（重大5件）。**うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
+          <t>**個票（1件ごとの回答データ）。**集計表は集計結果だけで個票がなく、問29×問31のクロス集計が作れない（依頼票D7）</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>2-15</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>介護保険の利用の有無による問31の再集計</t>
+          <t>アンケート調査結果及びヒアリング調査結果報告書の作成</t>
         </is>
       </c>
       <c r="D44" s="19" t="inlineStr">
@@ -5646,25 +5646,25 @@
       </c>
       <c r="F44" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G44" s="25" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H44" s="30" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I44" s="30" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="J44" s="30" t="n">
-        <v>30</v>
+        <v>33.4</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L44" s="31" t="inlineStr">
         <is>
@@ -5673,24 +5673,24 @@
       </c>
       <c r="M44" s="18" t="inlineStr">
         <is>
-          <t>**個票（1件ごとの回答データ）。**集計表は集計結果だけで個票がなく、問29×問31のクロス集計が作れない（依頼票D7）</t>
+          <t>**レビュー所見の反映（重大5件）、ヒアリング記録の完成**</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>アンケート調査結果及びヒアリング調査結果報告書の作成</t>
+          <t>回収票の点検・ナンバリング・データ入力</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -5700,30 +5700,30 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="F45" s="19" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="G45" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H45" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" s="30" t="n">
+        <v>60</v>
+      </c>
+      <c r="J45" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="I45" s="30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J45" s="30" t="n">
-        <v>33.4</v>
-      </c>
       <c r="K45" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L45" s="31" t="inlineStr">
         <is>
@@ -5732,24 +5732,24 @@
       </c>
       <c r="M45" s="18" t="inlineStr">
         <is>
-          <t>**レビュー所見の反映（重大5件）、ヒアリング記録の完成**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>回収票の点検・ナンバリング・データ入力</t>
+          <t>課題の抽出</t>
         </is>
       </c>
       <c r="D46" s="19" t="inlineStr">
@@ -5759,24 +5759,24 @@
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="F46" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G46" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H46" s="30" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I46" s="30" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J46" s="30" t="n">
         <v>40</v>
@@ -5791,24 +5791,24 @@
       </c>
       <c r="M46" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>調査結果・ヒアリング結果</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>2-12</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>課題の抽出</t>
+          <t>分析報告書のレビュー</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
@@ -5818,27 +5818,27 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="F47" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="G47" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H47" s="30" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I47" s="30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J47" s="30" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K47" s="19" t="n">
         <v>3</v>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="M47" s="18" t="inlineStr">
         <is>
-          <t>調査結果・ヒアリング結果</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -5862,12 +5862,12 @@
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>2-12</t>
+          <t>2-13</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>分析報告書のレビュー</t>
+          <t>目標値とアンケート設問の対応（MECEチェック）</t>
         </is>
       </c>
       <c r="D48" s="19" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>2-13</t>
+          <t>2-14</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>目標値とアンケート設問の対応（MECEチェック）</t>
+          <t>アンケートで不足する事項の洗い出しと対応方針</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>2-14</t>
+          <t>2-16</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>アンケートで不足する事項の洗い出しと対応方針</t>
+          <t>確認票の2枚化（町向け・事業所向け）</t>
         </is>
       </c>
       <c r="D50" s="19" t="inlineStr">
@@ -6018,7 +6018,7 @@
         <v>80</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L50" s="31" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
     <row r="52">
       <c r="A52" s="32" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 53.8％　対　予定進捗率 51.8％　乖離 +2.0ポイント</t>
+          <t>加重の実績進捗率 55.5％　対　予定進捗率 51.8％　乖離 +3.7ポイント</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
     <row r="54">
       <c r="A54" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">　遅れ 2件</t>
+          <t xml:space="preserve">　遅れ 1件</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
     <row r="56">
       <c r="A56" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">　前倒し 10件</t>
+          <t xml:space="preserve">　前倒し 11件</t>
         </is>
       </c>
     </row>
@@ -7863,25 +7863,25 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K24" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L24" s="21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N24" s="18" t="inlineStr">
         <is>
-          <t>**受領した確認票（15論点）を土台にする。**1枚のまま回すと回答者が担当外の行まで見ることになる</t>
+          <t>**令和8年10月7日に2冊を作成（23_障がいアンケート分析）。**確認依頼票（町）13件・5シート／照会票（事業所・関係機関）11件・4シート。**7論点は町と事業所の両方に関わるため、聞く内容を分けて両方に置いた。**宛先が答えられない語（定員・離職・支給決定台帳等）が混ざっていないことを機械で点検。自己点検10項目</t>
         </is>
       </c>
       <c r="O24" s="18" t="inlineStr">
         <is>
-          <t>2-15の結果（短期入所の照会の主題が変わる）</t>
+          <t>―</t>
         </is>
       </c>
     </row>
